--- a/notebooks/SHEM/tuning/NO3_model_whole.xlsx
+++ b/notebooks/SHEM/tuning/NO3_model_whole.xlsx
@@ -2663,43 +2663,43 @@
         <v>199.4013366699219</v>
       </c>
       <c r="AA19">
-        <v>19.75316619873047</v>
+        <v>29.83957862854004</v>
       </c>
       <c r="AB19">
-        <v>19.80757522583008</v>
+        <v>29.92176628112793</v>
       </c>
       <c r="AC19">
-        <v>19.8270092010498</v>
+        <v>29.95112419128418</v>
       </c>
       <c r="AD19">
-        <v>19.81009292602539</v>
+        <v>29.92557334899902</v>
       </c>
       <c r="AE19">
-        <v>19.80661010742188</v>
+        <v>29.92030906677246</v>
       </c>
       <c r="AF19">
-        <v>19.82015228271484</v>
+        <v>29.94076538085938</v>
       </c>
       <c r="AG19">
-        <v>19.82604217529297</v>
+        <v>29.94966506958008</v>
       </c>
       <c r="AH19">
-        <v>19.8157901763916</v>
+        <v>29.93417739868164</v>
       </c>
       <c r="AI19">
-        <v>19.81850242614746</v>
+        <v>29.93827438354492</v>
       </c>
       <c r="AJ19">
-        <v>19.84373474121094</v>
+        <v>29.97639274597168</v>
       </c>
       <c r="AK19">
-        <v>19.87884521484375</v>
+        <v>30.02943229675293</v>
       </c>
       <c r="AL19">
-        <v>19.86708641052246</v>
+        <v>30.01166534423828</v>
       </c>
       <c r="AM19">
-        <v>19.82098960876465</v>
+        <v>29.94203186035156</v>
       </c>
     </row>
     <row r="20" spans="1:39">
@@ -2770,43 +2770,43 @@
         <v>199.4013366699219</v>
       </c>
       <c r="AA20">
-        <v>19.63964462280273</v>
+        <v>29.83957862854004</v>
       </c>
       <c r="AB20">
-        <v>19.69373893737793</v>
+        <v>29.92176628112793</v>
       </c>
       <c r="AC20">
-        <v>19.71306228637695</v>
+        <v>29.95112419128418</v>
       </c>
       <c r="AD20">
-        <v>19.69624519348145</v>
+        <v>29.92557334899902</v>
       </c>
       <c r="AE20">
-        <v>19.69277954101562</v>
+        <v>29.92030906677246</v>
       </c>
       <c r="AF20">
-        <v>19.70624542236328</v>
+        <v>29.94076538085938</v>
       </c>
       <c r="AG20">
-        <v>19.71210098266602</v>
+        <v>29.94966506958008</v>
       </c>
       <c r="AH20">
-        <v>19.70190811157227</v>
+        <v>29.93417739868164</v>
       </c>
       <c r="AI20">
-        <v>19.70460510253906</v>
+        <v>29.93827438354492</v>
       </c>
       <c r="AJ20">
-        <v>19.72969436645508</v>
+        <v>29.97639274597168</v>
       </c>
       <c r="AK20">
-        <v>19.76460266113281</v>
+        <v>30.02943229675293</v>
       </c>
       <c r="AL20">
-        <v>19.75290679931641</v>
+        <v>30.01166534423828</v>
       </c>
       <c r="AM20">
-        <v>19.70707702636719</v>
+        <v>29.94203186035156</v>
       </c>
     </row>
     <row r="21" spans="1:39">
@@ -6669,43 +6669,43 @@
         <v>203.2755584716797</v>
       </c>
       <c r="AA54">
-        <v>10.10567092895508</v>
+        <v>23.46789741516113</v>
       </c>
       <c r="AB54">
-        <v>10.24470329284668</v>
+        <v>23.79076385498047</v>
       </c>
       <c r="AC54">
-        <v>10.24766826629639</v>
+        <v>23.79764938354492</v>
       </c>
       <c r="AD54">
-        <v>10.25113487243652</v>
+        <v>23.80570030212402</v>
       </c>
       <c r="AE54">
-        <v>10.26042747497559</v>
+        <v>23.82727813720703</v>
       </c>
       <c r="AF54">
-        <v>10.24510192871094</v>
+        <v>23.79168891906738</v>
       </c>
       <c r="AG54">
-        <v>10.23008441925049</v>
+        <v>23.75681495666504</v>
       </c>
       <c r="AH54">
-        <v>10.2501106262207</v>
+        <v>23.80332183837891</v>
       </c>
       <c r="AI54">
-        <v>10.2475643157959</v>
+        <v>23.79740905761719</v>
       </c>
       <c r="AJ54">
-        <v>10.30622291564941</v>
+        <v>23.93362808227539</v>
       </c>
       <c r="AK54">
-        <v>10.33738708496094</v>
+        <v>24.0059986114502</v>
       </c>
       <c r="AL54">
-        <v>10.30857181549072</v>
+        <v>23.93908309936523</v>
       </c>
       <c r="AM54">
-        <v>10.24475574493408</v>
+        <v>23.79088592529297</v>
       </c>
     </row>
     <row r="55" spans="1:39">
@@ -6785,43 +6785,43 @@
         <v>203.2755584716797</v>
       </c>
       <c r="AA55">
-        <v>3.265693664550781</v>
+        <v>23.46789741516113</v>
       </c>
       <c r="AB55">
-        <v>3.310623168945312</v>
+        <v>23.79076385498047</v>
       </c>
       <c r="AC55">
-        <v>3.311582565307617</v>
+        <v>23.79764938354492</v>
       </c>
       <c r="AD55">
-        <v>3.312702178955078</v>
+        <v>23.80570030212402</v>
       </c>
       <c r="AE55">
-        <v>3.315704345703125</v>
+        <v>23.82727813720703</v>
       </c>
       <c r="AF55">
-        <v>3.310752868652344</v>
+        <v>23.79168891906738</v>
       </c>
       <c r="AG55">
-        <v>3.305898666381836</v>
+        <v>23.75681495666504</v>
       </c>
       <c r="AH55">
-        <v>3.312370300292969</v>
+        <v>23.80332183837891</v>
       </c>
       <c r="AI55">
-        <v>3.311548233032227</v>
+        <v>23.79740905761719</v>
       </c>
       <c r="AJ55">
-        <v>3.33050537109375</v>
+        <v>23.93362808227539</v>
       </c>
       <c r="AK55">
-        <v>3.340574264526367</v>
+        <v>24.0059986114502</v>
       </c>
       <c r="AL55">
-        <v>3.331262588500977</v>
+        <v>23.93908309936523</v>
       </c>
       <c r="AM55">
-        <v>3.310640335083008</v>
+        <v>23.79088592529297</v>
       </c>
     </row>
     <row r="56" spans="1:39">
@@ -8983,43 +8983,43 @@
         <v>333.7438049316406</v>
       </c>
       <c r="AA74">
-        <v>23.09717559814453</v>
+        <v>28.32396507263184</v>
       </c>
       <c r="AB74">
-        <v>23.45407295227051</v>
+        <v>28.76162719726562</v>
       </c>
       <c r="AC74">
-        <v>23.45422744750977</v>
+        <v>28.76181793212891</v>
       </c>
       <c r="AD74">
-        <v>23.45441055297852</v>
+        <v>28.76204109191895</v>
       </c>
       <c r="AE74">
-        <v>23.45577239990234</v>
+        <v>28.76371192932129</v>
       </c>
       <c r="AF74">
-        <v>23.45402908325195</v>
+        <v>28.76157379150391</v>
       </c>
       <c r="AG74">
-        <v>23.4543571472168</v>
+        <v>28.7619743347168</v>
       </c>
       <c r="AH74">
-        <v>23.45418167114258</v>
+        <v>28.76176071166992</v>
       </c>
       <c r="AI74">
-        <v>23.4539909362793</v>
+        <v>28.76152610778809</v>
       </c>
       <c r="AJ74">
-        <v>23.49284934997559</v>
+        <v>28.80917930603027</v>
       </c>
       <c r="AK74">
-        <v>23.51816940307617</v>
+        <v>28.8402271270752</v>
       </c>
       <c r="AL74">
-        <v>23.49262046813965</v>
+        <v>28.80889701843262</v>
       </c>
       <c r="AM74">
-        <v>23.45394706726074</v>
+        <v>28.76147270202637</v>
       </c>
     </row>
     <row r="75" spans="1:39">
@@ -12691,43 +12691,43 @@
         <v>414.5332336425781</v>
       </c>
       <c r="AA107">
-        <v>21.30561447143555</v>
+        <v>28.35732269287109</v>
       </c>
       <c r="AB107">
-        <v>21.6303596496582</v>
+        <v>28.78955078125</v>
       </c>
       <c r="AC107">
-        <v>21.6303539276123</v>
+        <v>28.7895450592041</v>
       </c>
       <c r="AD107">
-        <v>21.63046264648438</v>
+        <v>28.7896900177002</v>
       </c>
       <c r="AE107">
-        <v>21.63125419616699</v>
+        <v>28.79074287414551</v>
       </c>
       <c r="AF107">
-        <v>21.63031768798828</v>
+        <v>28.78949546813965</v>
       </c>
       <c r="AG107">
-        <v>21.63031959533691</v>
+        <v>28.78949928283691</v>
       </c>
       <c r="AH107">
-        <v>21.63035774230957</v>
+        <v>28.78954887390137</v>
       </c>
       <c r="AI107">
-        <v>21.63034820556641</v>
+        <v>28.78953552246094</v>
       </c>
       <c r="AJ107">
-        <v>21.66333961486816</v>
+        <v>28.83344841003418</v>
       </c>
       <c r="AK107">
-        <v>21.68474197387695</v>
+        <v>28.86193466186523</v>
       </c>
       <c r="AL107">
-        <v>21.66341781616211</v>
+        <v>28.83355140686035</v>
       </c>
       <c r="AM107">
-        <v>21.63034439086914</v>
+        <v>28.78953170776367</v>
       </c>
     </row>
     <row r="108" spans="1:39">
@@ -17358,43 +17358,43 @@
         <v>184.8026580810547</v>
       </c>
       <c r="AA147">
-        <v>20.02184295654297</v>
+        <v>30.37422180175781</v>
       </c>
       <c r="AB147">
-        <v>19.99462509155273</v>
+        <v>30.33293151855469</v>
       </c>
       <c r="AC147">
-        <v>20.03592681884766</v>
+        <v>30.39558792114258</v>
       </c>
       <c r="AD147">
-        <v>20.0049934387207</v>
+        <v>30.34865760803223</v>
       </c>
       <c r="AE147">
-        <v>20.02435111999512</v>
+        <v>30.37802505493164</v>
       </c>
       <c r="AF147">
-        <v>20.03962516784668</v>
+        <v>30.40119743347168</v>
       </c>
       <c r="AG147">
-        <v>20.02202224731445</v>
+        <v>30.3744945526123</v>
       </c>
       <c r="AH147">
-        <v>20.01064872741699</v>
+        <v>30.35723876953125</v>
       </c>
       <c r="AI147">
-        <v>20.00704956054688</v>
+        <v>30.35177993774414</v>
       </c>
       <c r="AJ147">
-        <v>20.12564277648926</v>
+        <v>30.53169059753418</v>
       </c>
       <c r="AK147">
-        <v>20.14315032958984</v>
+        <v>30.55825233459473</v>
       </c>
       <c r="AL147">
-        <v>20.0554313659668</v>
+        <v>30.42517852783203</v>
       </c>
       <c r="AM147">
-        <v>20.02087593078613</v>
+        <v>30.37275314331055</v>
       </c>
     </row>
     <row r="148" spans="1:39">
@@ -18872,43 +18872,43 @@
         <v>199.4013366699219</v>
       </c>
       <c r="AA160">
-        <v>30.4288158416748</v>
+        <v>31.36610221862793</v>
       </c>
       <c r="AB160">
-        <v>30.43013763427734</v>
+        <v>31.36746406555176</v>
       </c>
       <c r="AC160">
-        <v>30.44559860229492</v>
+        <v>31.38340187072754</v>
       </c>
       <c r="AD160">
-        <v>30.41387367248535</v>
+        <v>31.35070037841797</v>
       </c>
       <c r="AE160">
-        <v>30.45094871520996</v>
+        <v>31.388916015625</v>
       </c>
       <c r="AF160">
-        <v>30.43903160095215</v>
+        <v>31.37663269042969</v>
       </c>
       <c r="AG160">
-        <v>30.44815826416016</v>
+        <v>31.38603973388672</v>
       </c>
       <c r="AH160">
-        <v>30.40298461914062</v>
+        <v>31.33947563171387</v>
       </c>
       <c r="AI160">
-        <v>30.41031455993652</v>
+        <v>31.34703063964844</v>
       </c>
       <c r="AJ160">
-        <v>30.4563102722168</v>
+        <v>31.39444351196289</v>
       </c>
       <c r="AK160">
-        <v>30.53702163696289</v>
+        <v>31.47764015197754</v>
       </c>
       <c r="AL160">
-        <v>30.47882843017578</v>
+        <v>31.41765594482422</v>
       </c>
       <c r="AM160">
-        <v>30.42068481445312</v>
+        <v>31.35772132873535</v>
       </c>
     </row>
     <row r="161" spans="1:39">
@@ -18988,43 +18988,43 @@
         <v>199.4013366699219</v>
       </c>
       <c r="AA161">
-        <v>21.12166404724121</v>
+        <v>31.36610221862793</v>
       </c>
       <c r="AB161">
-        <v>21.12258148193359</v>
+        <v>31.36746406555176</v>
       </c>
       <c r="AC161">
-        <v>21.13331604003906</v>
+        <v>31.38340187072754</v>
       </c>
       <c r="AD161">
-        <v>21.11129379272461</v>
+        <v>31.35070037841797</v>
       </c>
       <c r="AE161">
-        <v>21.13702774047852</v>
+        <v>31.388916015625</v>
       </c>
       <c r="AF161">
-        <v>21.12875556945801</v>
+        <v>31.37663269042969</v>
       </c>
       <c r="AG161">
-        <v>21.13508987426758</v>
+        <v>31.38603973388672</v>
       </c>
       <c r="AH161">
-        <v>21.10373306274414</v>
+        <v>31.33947563171387</v>
       </c>
       <c r="AI161">
-        <v>21.10882186889648</v>
+        <v>31.34703063964844</v>
       </c>
       <c r="AJ161">
-        <v>21.14074897766113</v>
+        <v>31.39444351196289</v>
       </c>
       <c r="AK161">
-        <v>21.19677352905273</v>
+        <v>31.47764015197754</v>
       </c>
       <c r="AL161">
-        <v>21.15637969970703</v>
+        <v>31.41765594482422</v>
       </c>
       <c r="AM161">
-        <v>21.11602020263672</v>
+        <v>31.35772132873535</v>
       </c>
     </row>
     <row r="162" spans="1:39">
@@ -20145,43 +20145,43 @@
         <v>119.6553649902344</v>
       </c>
       <c r="AA171">
-        <v>19.61636734008789</v>
+        <v>27.41762542724609</v>
       </c>
       <c r="AB171">
-        <v>19.6361026763916</v>
+        <v>27.44520950317383</v>
       </c>
       <c r="AC171">
-        <v>19.55246162414551</v>
+        <v>27.32830619812012</v>
       </c>
       <c r="AD171">
-        <v>19.6562614440918</v>
+        <v>27.47338485717773</v>
       </c>
       <c r="AE171">
-        <v>19.63396072387695</v>
+        <v>27.44221496582031</v>
       </c>
       <c r="AF171">
-        <v>19.65263938903809</v>
+        <v>27.46832275390625</v>
       </c>
       <c r="AG171">
-        <v>19.60380172729492</v>
+        <v>27.40006256103516</v>
       </c>
       <c r="AH171">
-        <v>19.63481140136719</v>
+        <v>27.44340705871582</v>
       </c>
       <c r="AI171">
-        <v>19.61550331115723</v>
+        <v>27.41641807556152</v>
       </c>
       <c r="AJ171">
-        <v>19.70687866210938</v>
+        <v>27.54413414001465</v>
       </c>
       <c r="AK171">
-        <v>19.65528869628906</v>
+        <v>27.47202491760254</v>
       </c>
       <c r="AL171">
-        <v>19.71871185302734</v>
+        <v>27.56067085266113</v>
       </c>
       <c r="AM171">
-        <v>19.61058616638184</v>
+        <v>27.4095458984375</v>
       </c>
     </row>
     <row r="172" spans="1:39">
@@ -22822,43 +22822,43 @@
         <v>203.2755584716797</v>
       </c>
       <c r="AA194">
-        <v>7.924250602722168</v>
+        <v>22.01428985595703</v>
       </c>
       <c r="AB194">
-        <v>7.842019081115723</v>
+        <v>21.78584098815918</v>
       </c>
       <c r="AC194">
-        <v>7.584004402160645</v>
+        <v>21.06905364990234</v>
       </c>
       <c r="AD194">
-        <v>7.854104042053223</v>
+        <v>21.81941795349121</v>
       </c>
       <c r="AE194">
-        <v>7.885870933532715</v>
+        <v>21.90766525268555</v>
       </c>
       <c r="AF194">
-        <v>7.85483455657959</v>
+        <v>21.82144737243652</v>
       </c>
       <c r="AG194">
-        <v>7.781355857849121</v>
+        <v>21.6173152923584</v>
       </c>
       <c r="AH194">
-        <v>7.854525566101074</v>
+        <v>21.82058715820312</v>
       </c>
       <c r="AI194">
-        <v>7.88786506652832</v>
+        <v>21.9132080078125</v>
       </c>
       <c r="AJ194">
-        <v>7.963379859924316</v>
+        <v>22.12299346923828</v>
       </c>
       <c r="AK194">
-        <v>8.013993263244629</v>
+        <v>22.26360511779785</v>
       </c>
       <c r="AL194">
-        <v>7.968103408813477</v>
+        <v>22.13611602783203</v>
       </c>
       <c r="AM194">
-        <v>7.84510612487793</v>
+        <v>21.79441833496094</v>
       </c>
     </row>
     <row r="195" spans="1:39">
@@ -24339,43 +24339,43 @@
         <v>174.2201538085938</v>
       </c>
       <c r="AA207">
-        <v>5.508842468261719</v>
+        <v>25.83625030517578</v>
       </c>
       <c r="AB207">
-        <v>5.54597282409668</v>
+        <v>26.0103931427002</v>
       </c>
       <c r="AC207">
-        <v>5.553928375244141</v>
+        <v>26.04771423339844</v>
       </c>
       <c r="AD207">
-        <v>5.612726211547852</v>
+        <v>26.3234691619873</v>
       </c>
       <c r="AE207">
-        <v>5.574722290039062</v>
+        <v>26.14522743225098</v>
       </c>
       <c r="AF207">
-        <v>5.524099349975586</v>
+        <v>25.90780830383301</v>
       </c>
       <c r="AG207">
-        <v>5.561479568481445</v>
+        <v>26.0831241607666</v>
       </c>
       <c r="AH207">
-        <v>5.574047088623047</v>
+        <v>26.14206123352051</v>
       </c>
       <c r="AI207">
-        <v>5.549228668212891</v>
+        <v>26.02566719055176</v>
       </c>
       <c r="AJ207">
-        <v>5.656482696533203</v>
+        <v>26.52868461608887</v>
       </c>
       <c r="AK207">
-        <v>5.620244979858398</v>
+        <v>26.35872840881348</v>
       </c>
       <c r="AL207">
-        <v>5.629156112670898</v>
+        <v>26.4005184173584</v>
       </c>
       <c r="AM207">
-        <v>5.579582214355469</v>
+        <v>26.16802787780762</v>
       </c>
     </row>
     <row r="208" spans="1:39">
@@ -26201,43 +26201,43 @@
         <v>333.7438049316406</v>
       </c>
       <c r="AA223">
-        <v>23.20587348937988</v>
+        <v>28.20026206970215</v>
       </c>
       <c r="AB223">
-        <v>23.47058296203613</v>
+        <v>28.52194213867188</v>
       </c>
       <c r="AC223">
-        <v>23.51435470581055</v>
+        <v>28.57513427734375</v>
       </c>
       <c r="AD223">
-        <v>23.57550239562988</v>
+        <v>28.64944267272949</v>
       </c>
       <c r="AE223">
-        <v>23.56818389892578</v>
+        <v>28.64054870605469</v>
       </c>
       <c r="AF223">
-        <v>23.51030731201172</v>
+        <v>28.57021522521973</v>
       </c>
       <c r="AG223">
-        <v>23.52149391174316</v>
+        <v>28.58381080627441</v>
       </c>
       <c r="AH223">
-        <v>23.5910758972168</v>
+        <v>28.66836738586426</v>
       </c>
       <c r="AI223">
-        <v>23.49803161621094</v>
+        <v>28.55529975891113</v>
       </c>
       <c r="AJ223">
-        <v>23.61199569702148</v>
+        <v>28.69379043579102</v>
       </c>
       <c r="AK223">
-        <v>23.55038261413574</v>
+        <v>28.61891746520996</v>
       </c>
       <c r="AL223">
-        <v>23.63037490844727</v>
+        <v>28.71612358093262</v>
       </c>
       <c r="AM223">
-        <v>23.58004570007324</v>
+        <v>28.65496444702148</v>
       </c>
     </row>
     <row r="224" spans="1:39">
@@ -28164,43 +28164,43 @@
         <v>384.956298828125</v>
       </c>
       <c r="AA240">
-        <v>21.92056655883789</v>
+        <v>28.3506031036377</v>
       </c>
       <c r="AB240">
-        <v>22.26771545410156</v>
+        <v>28.79958152770996</v>
       </c>
       <c r="AC240">
-        <v>22.27450180053711</v>
+        <v>28.80835914611816</v>
       </c>
       <c r="AD240">
-        <v>22.28814125061035</v>
+        <v>28.82600021362305</v>
       </c>
       <c r="AE240">
-        <v>22.23362922668457</v>
+        <v>28.75549697875977</v>
       </c>
       <c r="AF240">
-        <v>22.27944755554199</v>
+        <v>28.81475448608398</v>
       </c>
       <c r="AG240">
-        <v>22.26505661010742</v>
+        <v>28.796142578125</v>
       </c>
       <c r="AH240">
-        <v>22.26480102539062</v>
+        <v>28.79581260681152</v>
       </c>
       <c r="AI240">
-        <v>22.27681159973145</v>
+        <v>28.81134605407715</v>
       </c>
       <c r="AJ240">
-        <v>22.31567764282227</v>
+        <v>28.86161231994629</v>
       </c>
       <c r="AK240">
-        <v>22.33086776733398</v>
+        <v>28.88125801086426</v>
       </c>
       <c r="AL240">
-        <v>22.32951736450195</v>
+        <v>28.87951278686523</v>
       </c>
       <c r="AM240">
-        <v>22.25213050842285</v>
+        <v>28.7794246673584</v>
       </c>
     </row>
     <row r="241" spans="1:39">
@@ -34371,43 +34371,43 @@
         <v>160.8665618896484</v>
       </c>
       <c r="AA294">
-        <v>18.21846389770508</v>
+        <v>27.45204925537109</v>
       </c>
       <c r="AB294">
-        <v>18.39138793945312</v>
+        <v>27.71261405944824</v>
       </c>
       <c r="AC294">
-        <v>18.34528350830078</v>
+        <v>27.64314270019531</v>
       </c>
       <c r="AD294">
-        <v>18.42988586425781</v>
+        <v>27.77062606811523</v>
       </c>
       <c r="AE294">
-        <v>18.48293685913086</v>
+        <v>27.85056304931641</v>
       </c>
       <c r="AF294">
-        <v>18.43545150756836</v>
+        <v>27.77901268005371</v>
       </c>
       <c r="AG294">
-        <v>18.35663986206055</v>
+        <v>27.66025543212891</v>
       </c>
       <c r="AH294">
-        <v>18.39728736877441</v>
+        <v>27.72150421142578</v>
       </c>
       <c r="AI294">
-        <v>18.43005561828613</v>
+        <v>27.77088165283203</v>
       </c>
       <c r="AJ294">
-        <v>18.54353332519531</v>
+        <v>27.94187355041504</v>
       </c>
       <c r="AK294">
-        <v>18.56024932861328</v>
+        <v>27.9670581817627</v>
       </c>
       <c r="AL294">
-        <v>18.53408241271973</v>
+        <v>27.92763137817383</v>
       </c>
       <c r="AM294">
-        <v>18.44448852539062</v>
+        <v>27.79262924194336</v>
       </c>
     </row>
     <row r="295" spans="1:39">
@@ -36117,43 +36117,43 @@
         <v>319.6206970214844</v>
       </c>
       <c r="AA309">
-        <v>24.0894603729248</v>
+        <v>28.24356842041016</v>
       </c>
       <c r="AB309">
-        <v>24.43124198913574</v>
+        <v>28.64428901672363</v>
       </c>
       <c r="AC309">
-        <v>24.43162727355957</v>
+        <v>28.64474105834961</v>
       </c>
       <c r="AD309">
-        <v>24.43674850463867</v>
+        <v>28.6507453918457</v>
       </c>
       <c r="AE309">
-        <v>24.45590209960938</v>
+        <v>28.6732006072998</v>
       </c>
       <c r="AF309">
-        <v>24.43021011352539</v>
+        <v>28.6430778503418</v>
       </c>
       <c r="AG309">
-        <v>24.43835830688477</v>
+        <v>28.65263175964355</v>
       </c>
       <c r="AH309">
-        <v>24.43753433227539</v>
+        <v>28.65166473388672</v>
       </c>
       <c r="AI309">
-        <v>24.44293975830078</v>
+        <v>28.65800476074219</v>
       </c>
       <c r="AJ309">
-        <v>24.51406669616699</v>
+        <v>28.74139595031738</v>
       </c>
       <c r="AK309">
-        <v>24.53744697570801</v>
+        <v>28.76880836486816</v>
       </c>
       <c r="AL309">
-        <v>24.49858283996582</v>
+        <v>28.72324180603027</v>
       </c>
       <c r="AM309">
-        <v>24.43365097045898</v>
+        <v>28.6471118927002</v>
       </c>
     </row>
     <row r="310" spans="1:39">
@@ -42765,43 +42765,43 @@
         <v>333.3076782226562</v>
       </c>
       <c r="AA366">
-        <v>19.18224716186523</v>
+        <v>28.51340675354004</v>
       </c>
       <c r="AB366">
-        <v>19.44771957397461</v>
+        <v>28.90801811218262</v>
       </c>
       <c r="AC366">
-        <v>19.44690322875977</v>
+        <v>28.90680313110352</v>
       </c>
       <c r="AD366">
-        <v>19.44719886779785</v>
+        <v>28.9072437286377</v>
       </c>
       <c r="AE366">
-        <v>19.44876480102539</v>
+        <v>28.90957260131836</v>
       </c>
       <c r="AF366">
-        <v>19.44743728637695</v>
+        <v>28.90759658813477</v>
       </c>
       <c r="AG366">
-        <v>19.44734001159668</v>
+        <v>28.9074535369873</v>
       </c>
       <c r="AH366">
-        <v>19.44794273376465</v>
+        <v>28.90834999084473</v>
       </c>
       <c r="AI366">
-        <v>19.44681167602539</v>
+        <v>28.90666580200195</v>
       </c>
       <c r="AJ366">
-        <v>19.48188400268555</v>
+        <v>28.95879936218262</v>
       </c>
       <c r="AK366">
-        <v>19.49367141723633</v>
+        <v>28.97632026672363</v>
       </c>
       <c r="AL366">
-        <v>19.48269081115723</v>
+        <v>28.96000099182129</v>
       </c>
       <c r="AM366">
-        <v>19.4466667175293</v>
+        <v>28.90645217895508</v>
       </c>
     </row>
     <row r="367" spans="1:39">
@@ -43702,43 +43702,43 @@
         <v>60.65530395507812</v>
       </c>
       <c r="AA374">
-        <v>16.20808792114258</v>
+        <v>23.00350189208984</v>
       </c>
       <c r="AB374">
-        <v>15.72222900390625</v>
+        <v>22.31394195556641</v>
       </c>
       <c r="AC374">
-        <v>14.87194538116455</v>
+        <v>21.10716819763184</v>
       </c>
       <c r="AD374">
-        <v>16.00094795227051</v>
+        <v>22.70951652526855</v>
       </c>
       <c r="AE374">
-        <v>15.84957885742188</v>
+        <v>22.49468421936035</v>
       </c>
       <c r="AF374">
-        <v>15.94305515289307</v>
+        <v>22.62735176086426</v>
       </c>
       <c r="AG374">
-        <v>15.65819549560547</v>
+        <v>22.22306251525879</v>
       </c>
       <c r="AH374">
-        <v>16.06740760803223</v>
+        <v>22.80384063720703</v>
       </c>
       <c r="AI374">
-        <v>15.94500637054443</v>
+        <v>22.6301212310791</v>
       </c>
       <c r="AJ374">
-        <v>16.06536483764648</v>
+        <v>22.80093955993652</v>
       </c>
       <c r="AK374">
-        <v>16.05361747741699</v>
+        <v>22.78426933288574</v>
       </c>
       <c r="AL374">
-        <v>16.37510299682617</v>
+        <v>23.24054145812988</v>
       </c>
       <c r="AM374">
-        <v>15.96973419189453</v>
+        <v>22.66521644592285</v>
       </c>
     </row>
     <row r="375" spans="1:39">
@@ -47344,43 +47344,43 @@
         <v>199.4013366699219</v>
       </c>
       <c r="AA407">
-        <v>21.65798759460449</v>
+        <v>31.98189353942871</v>
       </c>
       <c r="AB407">
-        <v>21.654052734375</v>
+        <v>31.9760856628418</v>
       </c>
       <c r="AC407">
-        <v>21.64622497558594</v>
+        <v>31.96452713012695</v>
       </c>
       <c r="AD407">
-        <v>21.65493392944336</v>
+        <v>31.97738647460938</v>
       </c>
       <c r="AE407">
-        <v>21.67107582092285</v>
+        <v>32.001220703125</v>
       </c>
       <c r="AF407">
-        <v>21.64941596984863</v>
+        <v>31.96923637390137</v>
       </c>
       <c r="AG407">
-        <v>21.66397476196289</v>
+        <v>31.99073600769043</v>
       </c>
       <c r="AH407">
-        <v>21.66450881958008</v>
+        <v>31.99152565002441</v>
       </c>
       <c r="AI407">
-        <v>21.67437171936035</v>
+        <v>32.00608825683594</v>
       </c>
       <c r="AJ407">
-        <v>21.72616958618164</v>
+        <v>32.08257675170898</v>
       </c>
       <c r="AK407">
-        <v>21.75646209716797</v>
+        <v>32.1273078918457</v>
       </c>
       <c r="AL407">
-        <v>21.72796249389648</v>
+        <v>32.08522415161133</v>
       </c>
       <c r="AM407">
-        <v>21.65500450134277</v>
+        <v>31.97748947143555</v>
       </c>
     </row>
     <row r="408" spans="1:39">
@@ -48635,43 +48635,43 @@
         <v>160.8665618896484</v>
       </c>
       <c r="AA418">
-        <v>16.6904125213623</v>
+        <v>27.48543739318848</v>
       </c>
       <c r="AB418">
-        <v>16.63850021362305</v>
+        <v>27.39995002746582</v>
       </c>
       <c r="AC418">
-        <v>16.56608772277832</v>
+        <v>27.28070068359375</v>
       </c>
       <c r="AD418">
-        <v>16.67304992675781</v>
+        <v>27.45684242248535</v>
       </c>
       <c r="AE418">
-        <v>16.88159942626953</v>
+        <v>27.8002815246582</v>
       </c>
       <c r="AF418">
-        <v>16.63584136962891</v>
+        <v>27.39557266235352</v>
       </c>
       <c r="AG418">
-        <v>16.64435195922852</v>
+        <v>27.40958404541016</v>
       </c>
       <c r="AH418">
-        <v>16.64117813110352</v>
+        <v>27.40435981750488</v>
       </c>
       <c r="AI418">
-        <v>16.68870544433594</v>
+        <v>27.48262786865234</v>
       </c>
       <c r="AJ418">
-        <v>16.98138046264648</v>
+        <v>27.96459579467773</v>
       </c>
       <c r="AK418">
-        <v>17.00228118896484</v>
+        <v>27.99901580810547</v>
       </c>
       <c r="AL418">
-        <v>16.97805404663086</v>
+        <v>27.95911979675293</v>
       </c>
       <c r="AM418">
-        <v>16.6708984375</v>
+        <v>27.45330047607422</v>
       </c>
     </row>
     <row r="419" spans="1:39">
@@ -54937,43 +54937,43 @@
         <v>333.7438049316406</v>
       </c>
       <c r="AA473">
-        <v>24.35690498352051</v>
+        <v>25.36138153076172</v>
       </c>
       <c r="AB473">
-        <v>24.49313545227051</v>
+        <v>25.50322914123535</v>
       </c>
       <c r="AC473">
-        <v>26.34876823425293</v>
+        <v>27.43538856506348</v>
       </c>
       <c r="AD473">
-        <v>23.94560050964355</v>
+        <v>24.93311500549316</v>
       </c>
       <c r="AE473">
-        <v>24.14566612243652</v>
+        <v>25.14142990112305</v>
       </c>
       <c r="AF473">
-        <v>25.05483436584473</v>
+        <v>26.08809280395508</v>
       </c>
       <c r="AG473">
-        <v>23.78867340087891</v>
+        <v>24.76971626281738</v>
       </c>
       <c r="AH473">
-        <v>22.98270034790039</v>
+        <v>23.93050384521484</v>
       </c>
       <c r="AI473">
-        <v>24.17322158813477</v>
+        <v>25.17012214660645</v>
       </c>
       <c r="AJ473">
-        <v>25.84492874145508</v>
+        <v>26.91077041625977</v>
       </c>
       <c r="AK473">
-        <v>25.44268226623535</v>
+        <v>26.49193572998047</v>
       </c>
       <c r="AL473">
-        <v>25.26374626159668</v>
+        <v>26.30562019348145</v>
       </c>
       <c r="AM473">
-        <v>23.41810607910156</v>
+        <v>24.38386535644531</v>
       </c>
     </row>
     <row r="474" spans="1:39">
